--- a/lcr_analyses/clustering/carriers/CAST/cluster_summaries_pam.xlsx
+++ b/lcr_analyses/clustering/carriers/CAST/cluster_summaries_pam.xlsx
@@ -12,6 +12,10 @@
     <sheet name="k4" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="k5" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="k6" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="k7" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="k8" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="k9" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="k10" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4512,4 +4516,5820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>254</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3827830999136724</v>
+      </c>
+      <c r="E2" t="n">
+        <v>150.25</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.05118110236220472</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2086614173228346</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2992125984251969</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1062992125984252</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.3622047244094488</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.03543307086614173</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.07480314960629922</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1614173228346457</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.05118110236220472</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.06299212598425197</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1653543307086614</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.1456692913385827</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.03543307086614173</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.007874015748031496</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.8031496062992126</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.1417322834645669</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.007874015748031496</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.02362204724409449</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.6158527878917683</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.4927111224446428</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.1894678899082569</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.05237722048066876</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.654045148938065</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.1390459756041568</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1354672010124446</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.2929632603894801</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.1886792452830189</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>118</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>180</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1765046635871753</v>
+      </c>
+      <c r="E3" t="n">
+        <v>61.66666666666667</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08888888888888889</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.3055555555555556</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1722222222222222</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.3444444444444444</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.04444444444444445</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.01111111111111111</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.06111111111111111</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.04444444444444445</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.07222222222222222</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9388888888888889</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.07777777777777778</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.005555555555555556</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.02222222222222222</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.07222222222222222</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.005555555555555556</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.005555555555555556</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.6950537634408602</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.3934955050237969</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.1492318744473917</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.04119014704034184</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.6609794403198173</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1155844155844156</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.3179826885709238</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.4677083333333333</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.1920122887864823</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1238516645596291</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>62</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>145</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1384928716904277</v>
+      </c>
+      <c r="E4" t="n">
+        <v>47</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.02758620689655172</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1172413793103448</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.3655172413793104</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1793103448275862</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6206896551724138</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.04827586206896552</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.01379310344827586</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1655172413793103</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.06206896551724138</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.02758620689655172</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1241379310344828</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.04827586206896552</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.01379310344827586</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.04827586206896552</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1241379310344828</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9241379310344827</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.006896551724137931</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.4943181818181818</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.1337579617834395</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.02409638554216868</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.7433628318584071</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.06870229007633588</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1990049751243781</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>76</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>176</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3007440374690221</v>
+      </c>
+      <c r="E5" t="n">
+        <v>108</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.01704545454545454</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2159090909090909</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2272727272727273</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.09659090909090909</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.03977272727272727</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.07954545454545454</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1477272727272727</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.03409090909090909</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1477272727272727</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.005681818181818182</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.005681818181818182</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.1420454545454546</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.1534090909090909</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.005681818181818182</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.01704545454545454</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.6160838308760814</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.4685653134493234</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.1798206586794631</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.08823529411764706</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.6615191014798631</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1169838900292343</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1049689440993789</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.2447416315340843</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>41</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>121</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.3026315789473684</v>
+      </c>
+      <c r="E6" t="n">
+        <v>82</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.04958677685950413</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5867768595041323</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2231404958677686</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.04958677685950413</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.05785123966942149</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.01652892561983471</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.01652892561983471</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.6694214876033058</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1652892561983471</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.06611570247933884</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1487603305785124</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.008264462809917356</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.04958677685950413</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.03305785123966942</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6898395721925134</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.5466666666666666</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.04597701149425287</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.7062937062937062</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.3189655172413793</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.4570637119113574</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.1712707182320442</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>31</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3388888888888889</v>
+      </c>
+      <c r="E7" t="n">
+        <v>77</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.04597701149425287</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3448275862068966</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7126436781609196</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.09195402298850575</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.1609195402298851</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.7816091954022989</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.02298850574712644</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2183908045977012</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.02298850574712644</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1149425287356322</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.02298850574712644</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.06896551724137931</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.103448275862069</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.01149425287356322</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.5132075471698113</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5806451612903226</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1483739837398374</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.1043307086614173</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.7131630648330058</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.05813953488372095</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.2096774193548387</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.4291338582677166</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>57</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4940442427680091</v>
+      </c>
+      <c r="E8" t="n">
+        <v>137.25</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0108695652173913</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2173913043478261</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6847826086956522</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.2282608695652174</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0108695652173913</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.03260869565217391</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.03260869565217391</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.108695652173913</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1739130434782609</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.06521739130434782</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.1521739130434783</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.0108695652173913</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.0108695652173913</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.770996745857081</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.3711348256116606</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.1160800320759306</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.05419501133786848</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.7455035971223021</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.3002806188383857</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.175843253968254</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.4589955175224124</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.1181177468072704</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.194769207972142</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>61</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>209</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3388888888888889</v>
+      </c>
+      <c r="E2" t="n">
+        <v>130.75</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04784688995215311</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2344497607655502</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2583732057416268</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.3923444976076555</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.04784688995215311</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.07177033492822966</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.03827751196172249</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0430622009569378</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.1244019138755981</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.004784688995215311</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.0430622009569378</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.009569377990430622</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.9043062200956937</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.1435406698564593</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.004784688995215311</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.009569377990430622</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.03349282296650718</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.5982142857142857</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.4950166112956811</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.1890547263681592</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.05165289256198347</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.6578947368421053</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.1169811320754717</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1258278145695364</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.2504504504504504</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.1970338983050847</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>56</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6271186440677966</v>
+      </c>
+      <c r="E3" t="n">
+        <v>207</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.03883495145631068</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6990291262135923</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.05825242718446602</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0970873786407767</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.1650485436893204</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.1650485436893204</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1067961165048544</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1067961165048544</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.009708737864077669</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.08737864077669903</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.0970873786407767</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.5922330097087378</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.116504854368932</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.04854368932038835</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.1359223300970874</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.009708737864077669</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.009708737864077669</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.4889589905362776</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.1801801801801802</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.6552567237163814</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1869639794168096</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1746031746031746</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.383419689119171</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.01424287856071964</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1425855513307985</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>210</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2215637324830075</v>
+      </c>
+      <c r="E4" t="n">
+        <v>68</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0761904761904762</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1761904761904762</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3666666666666666</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.009523809523809525</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.06190476190476191</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0761904761904762</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.9095238095238095</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.06190476190476191</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1476190476190476</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.009523809523809525</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.004761904761904762</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.004761904761904762</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.6857142857142857</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.4058697686856532</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.1519014385415183</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.04113618049959709</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.6629209966195067</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.12858253433532</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.2964375</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.4560661764705882</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.1569767441860465</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.135027885027885</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2908076975027793</v>
+      </c>
+      <c r="E5" t="n">
+        <v>105.4583333333333</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.01333333333333333</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1533333333333333</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2066666666666667</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.09333333333333334</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7466666666666667</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.04666666666666667</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.08666666666666667</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1266666666666667</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.006666666666666667</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.8066666666666666</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.006666666666666667</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.6047215098309989</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.4685653134493234</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.1803628825082745</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.09110231017546222</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1076519819736963</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.2336424138188888</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0.002893383212532148</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1991957390959314</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>117</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2452830188679245</v>
+      </c>
+      <c r="E6" t="n">
+        <v>75</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2478632478632479</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.06837606837606838</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.3076923076923077</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.05128205128205128</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0170940170940171</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0170940170940171</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.7863247863247863</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.188034188034188</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.09401709401709402</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.05982905982905983</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.008547008547008548</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.008547008547008548</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.04273504273504274</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.5522388059701493</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1612903225806452</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.04597701149425287</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.3209876543209876</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.1376811594202899</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.4624624624624625</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.1836734693877551</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1019900497512438</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>65</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3134796238244514</v>
+      </c>
+      <c r="E7" t="n">
+        <v>69</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.01538461538461539</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2461538461538462</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7846153846153846</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.03076923076923077</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.1230769230769231</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.676923076923077</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.03076923076923077</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2615384615384616</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.04615384615384616</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1076923076923077</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.01538461538461539</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1384615384615385</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.4228187919463087</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.6577181208053692</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1470588235294118</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.7327586206896551</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.0851063829787234</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.03355704697986577</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.1222222222222222</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.05405405405405406</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.4895833333333333</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>39</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5023482785110692</v>
+      </c>
+      <c r="E8" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01282051282051282</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2051282051282051</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6923076923076923</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.08974358974358974</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.2564102564102564</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.9102564102564102</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.01282051282051282</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.05128205128205128</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.1282051282051282</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1282051282051282</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.08974358974358974</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.08974358974358974</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.01282051282051282</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.7716701902748414</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.3614814814814815</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.1056249686386672</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.05235745614035088</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.7625078173858661</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.3040575243965075</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1702516011978927</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.4572368421052632</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.1355311355311355</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.205303529229458</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>53</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>123</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1241379310344828</v>
+      </c>
+      <c r="E9" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.03252032520325204</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1056910569105691</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3170731707317073</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1869918699186992</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6260162601626016</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01626016260162602</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1707317073170732</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.03252032520325204</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.03252032520325204</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.1056910569105691</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.02439024390243903</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.008130081300813009</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.05691056910569105</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.1056910569105691</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.9512195121951219</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.008130081300813009</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.4939759036144578</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.1322645290581163</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.02277227722772277</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.7468354430379747</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.06633663366336634</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.06818181818181819</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.1346153846153846</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1951219512195122</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>68</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>176</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3292841179439118</v>
+      </c>
+      <c r="E2" t="n">
+        <v>132</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.04545454545454546</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2443181818181818</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2215909090909091</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.09659090909090909</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2954545454545455</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.01704545454545454</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1761363636363636</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.03409090909090909</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.03977272727272727</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.05113636363636364</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.01704545454545454</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.05113636363636364</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.005681818181818182</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.8579545454545454</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.1136363636363636</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.005681818181818182</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.03977272727272727</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.5928401663695781</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.500317662007624</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.1905989125381521</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.05525030525030525</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.65424415240929</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.1146141215106732</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1161105493764745</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.2298850574712644</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.2028985507246377</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>86</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>45</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>104</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3940653873489695</v>
+      </c>
+      <c r="E3" t="n">
+        <v>111.875</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7211538461538461</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1923076923076923</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.9326923076923077</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.09615384615384616</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1826923076923077</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.1346153846153846</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.08653846153846154</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.8365384615384616</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1153846153846154</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.01923076923076923</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.7115384615384616</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.3365384615384616</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.01923076923076923</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.01923076923076923</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.6277836624283116</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.4695736789817008</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.1714139062255912</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.05027345445220342</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.6621841388050829</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1430169383189517</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.2038645245332175</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.3432347388294525</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.0388584059343499</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1751555042663001</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>33</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>151</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1551362683438155</v>
+      </c>
+      <c r="E4" t="n">
+        <v>59</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.08609271523178808</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.152317880794702</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2582781456953642</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1854304635761589</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.271523178807947</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.03973509933774835</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.006622516556291391</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.05298013245033113</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.03311258278145696</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0728476821192053</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.9735099337748344</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.03311258278145696</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.006622516556291391</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.03311258278145696</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.02649006622516556</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.08609271523178808</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.006622516556291391</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.01324503311258278</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.70625</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.3818181818181818</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.1475409836065574</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.0410958904109589</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.6578947368421053</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.1012658227848101</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.330188679245283</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.4754098360655737</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.2207792207792208</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1206896551724138</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>56</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>140</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2645821077876827</v>
+      </c>
+      <c r="E5" t="n">
+        <v>95</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1785714285714286</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2357142857142857</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.08571428571428572</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6785714285714286</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.07857142857142857</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.03571428571428571</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1071428571428571</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.04285714285714286</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.07857142857142857</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.007142857142857143</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.007142857142857143</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.6020408163265306</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.4715145900880037</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.1739130434782609</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.09386748120300752</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.6679298642533936</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.09296832082036258</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.2050404131118096</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.006750507220432034</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.2013636363636364</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>84</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>105</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.296551724137931</v>
+      </c>
+      <c r="E6" t="n">
+        <v>78</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.1523809523809524</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.01904761904761905</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.01904761904761905</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.7047619047619048</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.01904761904761905</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6869565217391305</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.5818181818181818</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.05000000000000001</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.7022900763358778</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.3255813953488372</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.1391304347826087</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.460431654676259</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.1851851851851852</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.09281437125748504</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3405797101449275</v>
+      </c>
+      <c r="E7" t="n">
+        <v>75</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.05063291139240506</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3544303797468354</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7215189873417721</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1012658227848101</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.1645569620253164</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.8227848101265823</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.02531645569620253</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2025316455696203</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.02531645569620253</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1139240506329114</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.06329113924050633</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.0379746835443038</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1139240506329114</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.0379746835443038</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.5132075471698113</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5934959349593496</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1484848484848485</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.1056910569105691</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.7131630648330058</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.05797101449275362</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.2096774193548387</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.06306306306306306</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.4326241134751773</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>53</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>82</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5023482785110692</v>
+      </c>
+      <c r="E8" t="n">
+        <v>136.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01219512195121951</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6707317073170732</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.07317073170731707</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.1951219512195122</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.01219512195121951</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.8658536585365854</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.02439024390243903</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.03658536585365853</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.08536585365853659</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.08536585365853659</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.07317073170731707</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.07317073170731707</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.1707317073170732</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.01219512195121951</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.7730257224286591</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.3639909871849036</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.1130252100840336</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.05365319204604919</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.7550622068694357</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.3040575243965075</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.156034906588004</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.4527185631286578</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.1355311355311355</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.2067147613762487</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>58</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>123</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1160714285714286</v>
+      </c>
+      <c r="E9" t="n">
+        <v>43</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02439024390243903</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0975609756097561</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.3414634146341464</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1788617886178862</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.5691056910569106</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.01626016260162602</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1707317073170732</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.05691056910569105</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.01626016260162602</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.04065040650406504</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.02439024390243903</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.01626016260162602</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.04065040650406504</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.08130081300813008</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.943089430894309</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.008130081300813009</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.3653846153846154</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.02173913043478261</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.7611464968152867</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.05607476635514018</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.1325301204819277</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>67</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>95</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.4206500956022944</v>
+      </c>
+      <c r="E10" t="n">
+        <v>155</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.03157894736842105</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.2631578947368421</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1263157894736842</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.04210526315789474</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.3052631578947368</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.06315789473684211</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.04210526315789474</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.07368421052631578</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.06315789473684211</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.06315789473684211</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.06315789473684211</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.9052631578947369</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.04210526315789474</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.09473684210526316</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.01052631578947368</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.6856287425149701</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.4875</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.1774691358024691</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.04938271604938271</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.6756756756756757</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.2033898305084746</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.2018927444794952</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.4049079754601227</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>-0.007092198581560284</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.1295896328293737</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>178</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3105779356381745</v>
+      </c>
+      <c r="E2" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.03932584269662921</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1910112359550562</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2359550561797753</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0898876404494382</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.3314606741573033</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.02247191011235955</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.05617977528089887</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1741573033707865</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.02808988764044944</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.03370786516853932</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.06179775280898876</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.0449438202247191</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.005617977528089887</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.0449438202247191</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.005617977528089887</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.8876404494382022</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.06741573033707865</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.005617977528089887</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.03370786516853932</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.5991071428571428</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.4986486486486487</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.189933966604422</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.05334441980783444</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.6579914860681115</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.1163169433134983</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1218963831867058</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.2389567669172932</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.2030752916224814</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>82</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.08544345316189977</v>
+      </c>
+      <c r="E3" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1282051282051282</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.01282051282051282</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.02564102564102564</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.01282051282051282</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.9615384615384616</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.02564102564102564</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.01282051282051282</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.01282051282051282</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.7434164934164934</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.3543580470162748</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.1458721934369603</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.04228707564026206</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.6495037220843672</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.09011038522189682</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.3813852813852813</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.5033333333333334</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.2937254901960784</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1224489795918367</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>31</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>81</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="E4" t="n">
+        <v>121.3333333333333</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.06172839506172839</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2469135802469136</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7160493827160493</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.9259259259259259</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.08641975308641975</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.1604938271604938</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1851851851851852</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1234567901234568</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1975308641975309</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.02469135802469136</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.8148148148148148</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.691358024691358</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.01234567901234568</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.02469135802469136</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.5868811100599181</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.4756554307116105</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.1809872029250457</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.0492676431424767</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.1332007952286282</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.1653005464480874</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.3064516129032258</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0.02313883299798792</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1763565891472868</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>134</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2905125093646195</v>
+      </c>
+      <c r="E5" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.01492537313432836</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1417910447761194</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2014925373134328</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.07462686567164178</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6865671641791045</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.02985074626865672</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.08208955223880597</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1417910447761194</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.02238805970149254</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.08208955223880597</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.08955223880597014</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.09701492537313433</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.007462686567164179</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.8582089552238806</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.1044776119402985</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.1044776119402985</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.007462686567164179</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.01492537313432836</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.6047215098309989</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.4736305443833909</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.1814285714285714</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.09487973326982616</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.6513157894736843</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.09424284183126627</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.2065775401069519</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1991957390959314</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>79</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>105</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2620689655172414</v>
+      </c>
+      <c r="E6" t="n">
+        <v>78</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.3238095238095238</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2761904761904762</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.2571428571428571</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.01904761904761905</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.01904761904761905</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.819047619047619</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1714285714285714</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.009523809523809525</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.009523809523809525</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.0380952380952381</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6898395721925134</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.5679611650485437</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1699029126213592</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.04597701149425287</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.7055214723926381</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.3209876543209876</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.1411290322580645</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.456140350877193</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.1836734693877551</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.09462915601023018</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>74</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3211512004615453</v>
+      </c>
+      <c r="E7" t="n">
+        <v>75</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.04054054054054054</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3108108108108108</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7297297297297297</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1081081081081081</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.1621621621621622</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.8513513513513513</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.02702702702702703</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.1486486486486487</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.02702702702702703</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.06756756756756757</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.02702702702702703</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.08108108108108109</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.02702702702702703</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1081081081081081</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.04054054054054054</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.5213096559378468</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5870705481248362</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1484294161123429</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.1084010840108401</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.1581451612903226</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.05676328502415458</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.2091865357643758</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.06651884700665188</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.4361396429444852</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>68</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5455893987341772</v>
+      </c>
+      <c r="E8" t="n">
+        <v>137.25</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01470588235294118</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2058823529411765</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6617647058823529</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.07352941176470588</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.2205882352941176</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.9705882352941176</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.01470588235294118</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.01470588235294118</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.04411764705882353</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.08823529411764706</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1029411764705882</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.07352941176470588</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.04411764705882353</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.1617647058823529</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.01470588235294118</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.7788183890577507</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.3442923197021558</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.094875</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.05326189725811535</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.7697596737810168</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.3180176565008026</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1642496762357004</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.4610507246376812</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.1611067359043142</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.2118793916177132</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>51</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>115</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.103448275862069</v>
+      </c>
+      <c r="E9" t="n">
+        <v>40</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.03478260869565217</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1130434782608696</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2869565217391304</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.191304347826087</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.5565217391304348</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.05217391304347826</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.008695652173913044</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.1739130434782609</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.02608695652173913</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.02608695652173913</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.04347826086956522</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.01739130434782609</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.008695652173913044</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.05217391304347826</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.04347826086956522</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.9304347826086956</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.008695652173913044</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.3548387096774194</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.1153846153846154</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.02083333333333333</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.7702702702702703</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.1276595744680851</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>62</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>111</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.407035175879397</v>
+      </c>
+      <c r="E10" t="n">
+        <v>153.3333333333333</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.03603603603603604</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6216216216216216</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.08108108108108109</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.07207207207207207</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.1801801801801802</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.09009009009009009</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.09009009009009009</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.1081081081081081</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0990990990990991</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.08108108108108109</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.6396396396396397</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.09009009009009009</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.06306306306306306</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.1081081081081081</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.009009009009009009</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.6651884700665188</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.4898785425101215</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.174496644295302</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.6738035264483627</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.1948051948051948</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.1922246220302376</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.4013605442176871</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.006451612903225806</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.126984126984127</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>111</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.2631578947368421</v>
+      </c>
+      <c r="E11" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.08108108108108109</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1531531531531531</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.7027027027027027</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1531531531531531</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.1171171171171171</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.08108108108108109</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.009009009009009009</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.07207207207207207</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.08108108108108109</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.09009009009009009</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.8828828828828829</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.03603603603603604</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.03603603603603604</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.0990990990990991</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.1171171171171171</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.009009009009009009</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.01801801801801802</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.6820512820512821</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.4316239316239316</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.1585365853658537</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.04332129963898917</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.6625766871165644</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.148936170212766</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.2888888888888889</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.4468085106382979</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-0.1411764705882353</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.1434262948207171</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>